--- a/site-dsidd/docs/references/references_dsidd_v2.xlsx
+++ b/site-dsidd/docs/references/references_dsidd_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arnau\d-sidd Dropbox\Equipe\sites internet\d-sidd.github.io\site-dsidd\references\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arnau\d-sidd Dropbox\Equipe\sites internet\Site rmarkdown\site-dsidd\references\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{130D71A8-2BCA-4AC3-BF84-41C029728FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCAA659-A2B9-4008-A52D-D5C751BE3B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A1639DB-56E8-489A-8363-79F7F85173AB}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$T$49</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,240 +39,363 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="166">
+  <si>
+    <t>Origine expérience</t>
+  </si>
+  <si>
+    <t>Client final</t>
+  </si>
+  <si>
+    <t>Partenaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Désignation de la référence               </t>
+  </si>
   <si>
     <t>Année d’exécution</t>
   </si>
   <si>
+    <t>num</t>
+  </si>
+  <si>
     <t>Montant HT</t>
   </si>
   <si>
+    <t>Arnaud</t>
+  </si>
+  <si>
+    <t>Emmanuelle</t>
+  </si>
+  <si>
+    <t>Afficher Arnaud</t>
+  </si>
+  <si>
+    <t>T_Bien-être territorial, santé et accès aux soins</t>
+  </si>
+  <si>
+    <t>T_Développement économique durable des territoires</t>
+  </si>
+  <si>
+    <t>T_Emploi/ Formation</t>
+  </si>
+  <si>
+    <t>T_Impact économique, social et environnemental</t>
+  </si>
+  <si>
+    <t>T_Mesure du potentiel sur les territoires</t>
+  </si>
+  <si>
+    <t>Veille et recherche</t>
+  </si>
+  <si>
+    <t>start_dates</t>
+  </si>
+  <si>
+    <t>end_dates</t>
+  </si>
+  <si>
+    <t>Projets</t>
+  </si>
+  <si>
+    <t>selec</t>
+  </si>
+  <si>
+    <t>d-sidd</t>
+  </si>
+  <si>
+    <t>Grand Narbonne</t>
+  </si>
+  <si>
+    <t>Novascopia</t>
+  </si>
+  <si>
+    <t>Diagnostic de la santé, la qualité de vie et du bien-être</t>
+  </si>
+  <si>
+    <t>Oui</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Région Auvergne-Rhône-Alpes</t>
+  </si>
+  <si>
+    <t>Terre d'Avance</t>
+  </si>
+  <si>
+    <t>Observatoire de la qualité de vie</t>
+  </si>
+  <si>
+    <t>Département des Alpes-Maritimes</t>
+  </si>
+  <si>
+    <t>La Pitaya</t>
+  </si>
+  <si>
+    <t>Baromètre des activités de pleine nature</t>
+  </si>
+  <si>
+    <t>Canet-en-Roussillon</t>
+  </si>
+  <si>
+    <t>Territoire &amp; Sens</t>
+  </si>
+  <si>
+    <t>Analyse des besoins sociaux</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>Carqueiranne</t>
+  </si>
+  <si>
+    <t>CEISS Consultants</t>
+  </si>
+  <si>
+    <t>EID Méditerranée</t>
+  </si>
+  <si>
+    <t>Enalys</t>
+  </si>
+  <si>
+    <t>Observatoire sur la perception de la nuisance liée aux moustiques</t>
+  </si>
+  <si>
+    <t>La Londe-les-Maures</t>
+  </si>
+  <si>
+    <t>MedTrucks</t>
+  </si>
+  <si>
+    <t>Application interactive dédiée à la lutte contre le désert médicaux</t>
+  </si>
+  <si>
+    <t>2018 à 2020</t>
+  </si>
+  <si>
+    <t>E-Meuse santé</t>
+  </si>
+  <si>
+    <t>Diagnostic des déserts médicaux et modélisation de l’offre de téléconsultation</t>
+  </si>
+  <si>
+    <t>2020 – 2023</t>
+  </si>
+  <si>
+    <t>PARM</t>
+  </si>
+  <si>
+    <t>IRAM</t>
+  </si>
+  <si>
+    <t>Analyse du risque agricole pour l’IFAD Platform for Agricultural Risk Management</t>
+  </si>
+  <si>
     <t>Région Occitanie</t>
   </si>
   <si>
-    <t>PARM</t>
-  </si>
-  <si>
-    <t>Analyse du risque agricole pour l’IFAD Platform for Agricultural Risk Management</t>
+    <t>Diagnostic de l’offre d’accompagnement de l’ESS</t>
   </si>
   <si>
     <t>Loire Forez agglomération</t>
   </si>
   <si>
+    <t>Logis-Cité, Oxalys</t>
+  </si>
+  <si>
+    <t>Analyse des déterminants du choix de résidence des ménages</t>
+  </si>
+  <si>
     <t>Réseau Rural Français</t>
   </si>
   <si>
+    <t>Boréal</t>
+  </si>
+  <si>
+    <t>Automatisation du baromètre de la coopération LEADER</t>
+  </si>
+  <si>
+    <t>Région Sud</t>
+  </si>
+  <si>
+    <t>Indicateurs de suivi socio-économique stratégique</t>
+  </si>
+  <si>
+    <t>SIAO 13</t>
+  </si>
+  <si>
+    <t>Étude sur la mise en cohérence des fonctionnements du Services Intégré d'Accueil et d'Orientation (SIAO) avec les exigences du Logement d'Abord</t>
+  </si>
+  <si>
     <t>AID Observatoire</t>
   </si>
   <si>
+    <t>Expérience professionnelle au sein du cabinet AID Observatoire</t>
+  </si>
+  <si>
     <t>Analyse des flux de consommation des ménages sur plusieurs dizaines de territoires</t>
   </si>
   <si>
     <t>2008 à 2010</t>
   </si>
   <si>
+    <t>n.c</t>
+  </si>
+  <si>
+    <t>Expérience professionnelle au sein du cabinet CRT Bretagne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tourisme durable :  Impact économique, environnemental et social du tourisme sur les destinations bretonnes </t>
+  </si>
+  <si>
+    <t>Cantal</t>
+  </si>
+  <si>
+    <t>Evaluation du poids économique de la pêche dans le cantal</t>
+  </si>
+  <si>
+    <t>Région Nouvelle-Aquitaine</t>
+  </si>
+  <si>
+    <t>terre d'Avance</t>
+  </si>
+  <si>
+    <t>Evaluation du poids économique de la pêche en Nouvelle-Aquitaine</t>
+  </si>
+  <si>
+    <t>Région Pays de la Loire</t>
+  </si>
+  <si>
+    <t>Evaluation du poids économique de la pêche en Pays de la Loire</t>
+  </si>
+  <si>
+    <t>ANCT - PETR Centre-Ouest Aveyron</t>
+  </si>
+  <si>
     <t>Diagnostic des flux et des interactions interterritoriales</t>
   </si>
   <si>
     <t>CNRS</t>
   </si>
   <si>
+    <t>Data Terra, Chrysalide</t>
+  </si>
+  <si>
     <t>Cartographie des activités de valorisation non académique des chercheurs</t>
   </si>
   <si>
-    <t>Région Pays de la Loire</t>
-  </si>
-  <si>
-    <t>Evaluation du poids économique de la pêche en Pays de la Loire</t>
-  </si>
-  <si>
-    <t>Région Nouvelle-Aquitaine</t>
-  </si>
-  <si>
-    <t>Evaluation du poids économique de la pêche en Nouvelle-Aquitaine</t>
-  </si>
-  <si>
-    <t>Cantal</t>
-  </si>
-  <si>
-    <t>Evaluation du poids économique de la pêche dans le cantal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tourisme durable :  Impact économique, environnemental et social du tourisme sur les destinations bretonnes </t>
+    <t>ANCT – Région Sud</t>
+  </si>
+  <si>
+    <t>Teriteo</t>
+  </si>
+  <si>
+    <t>Elaboration d’outils nationaux liés à la gouvernance et à la mise en œuvre des fonds européens</t>
+  </si>
+  <si>
+    <t>Clean Atlantic, Union Européenne</t>
+  </si>
+  <si>
+    <t>Cedre</t>
+  </si>
+  <si>
+    <t>Collecte et traitement des données sur la collecte, le traitement et la valorisation des déchets marins sur le littoral atlantique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ministère de la Pêche et de l’Economie Maritime de Guinée - AFD </t>
+  </si>
+  <si>
+    <t>Tero</t>
+  </si>
+  <si>
+    <t>Etude d’impact du projet PISCOFAM</t>
+  </si>
+  <si>
+    <t>DREAL Occitanie</t>
+  </si>
+  <si>
+    <t>Structuration des données de suivi du Plan de Protection de l’Atmosphère de la zone urbaine de Nîmes</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Cap Métiers – Nouvelle-Aquitaine</t>
+  </si>
+  <si>
+    <t>TERRITEC</t>
+  </si>
+  <si>
+    <t>Optimisation d’un outil de projections macro-économiques par métier à moyen terme</t>
+  </si>
+  <si>
+    <t>2022-2023</t>
+  </si>
+  <si>
+    <t>D-SIDD</t>
+  </si>
+  <si>
+    <t>Applications interactives et libres de diagnostic d’accessibilité aux circuits-courts, aux tiers-lieux et végétalisation de l’espace urbain</t>
+  </si>
+  <si>
+    <t>Accès libre</t>
+  </si>
+  <si>
+    <t>Région Centre-Val-de-Loire</t>
+  </si>
+  <si>
+    <t>Dowel Stratégie</t>
+  </si>
+  <si>
+    <t>Analyse de la chaîne d’approvisionnement de la restauration collective et réalisation d’une application interactive collaborative</t>
   </si>
   <si>
     <t>CC du Grand Pic Saint Loup</t>
   </si>
   <si>
+    <t>CIVAM-LR</t>
+  </si>
+  <si>
+    <t>Mesure du potentiel de consommation en circuits courts</t>
+  </si>
+  <si>
     <t>Relais d’Entreprises</t>
   </si>
   <si>
     <t>Réalisation d’une application de mesure du potentiel de télétravail en France</t>
   </si>
   <si>
-    <t>D-SIDD</t>
-  </si>
-  <si>
-    <t>Applications interactives et libres de diagnostic d’accessibilité aux circuits-courts, aux tiers-lieux et végétalisation de l’espace urbain</t>
-  </si>
-  <si>
-    <t>Région Centre-Val-de-Loire</t>
-  </si>
-  <si>
-    <t>Analyse des besoins sociaux</t>
-  </si>
-  <si>
-    <t>EID Méditerranée</t>
-  </si>
-  <si>
-    <t>Observatoire sur la perception de la nuisance liée aux moustiques</t>
-  </si>
-  <si>
-    <t>Département des Alpes-Maritimes</t>
-  </si>
-  <si>
-    <t>Baromètre des activités de pleine nature</t>
-  </si>
-  <si>
-    <t>MedTrucks</t>
-  </si>
-  <si>
-    <t>2018 à 2020</t>
-  </si>
-  <si>
-    <t>Grand Narbonne</t>
-  </si>
-  <si>
-    <t>Région Auvergne-Rhône-Alpes</t>
-  </si>
-  <si>
-    <t>E-Meuse santé</t>
-  </si>
-  <si>
-    <t>Origine expérience</t>
-  </si>
-  <si>
-    <t>d-sidd</t>
-  </si>
-  <si>
-    <t>Arnaud</t>
+    <t>Mairie de Prades-le-Lez</t>
+  </si>
+  <si>
+    <t>Prévision des effectifs scolaires</t>
+  </si>
+  <si>
+    <t>Labex entreprendre</t>
+  </si>
+  <si>
+    <t>Expérience professionnelle au sein du Labex Entreprendre, Université de Montpellier</t>
   </si>
   <si>
     <t>How do research-based start-ups overcome the Valley of Death?. Bessiere, Veronique &amp; Gomez Breysse, Marie &amp; Messeghem, Karim &amp; Milet, Arnaud &amp; Sammut, Sylvie.</t>
   </si>
   <si>
-    <t>2020 – 2023</t>
-  </si>
-  <si>
-    <t>Labex entreprendre</t>
-  </si>
-  <si>
-    <t>Oui</t>
-  </si>
-  <si>
-    <t>Mairie de Prades-le-Lez</t>
-  </si>
-  <si>
-    <t>Optimisation d’un outil de projections macro-économiques par métier à moyen terme</t>
-  </si>
-  <si>
-    <t>2022-2023</t>
-  </si>
-  <si>
-    <t>Cap Métiers – Nouvelle-Aquitaine</t>
-  </si>
-  <si>
-    <t>Indicateurs de suivi socio-économique stratégique</t>
-  </si>
-  <si>
-    <t>Région Sud</t>
-  </si>
-  <si>
-    <t>ANCT – Région Sud</t>
-  </si>
-  <si>
-    <t>Collecte et traitement des données sur la collecte, le traitement et la valorisation des déchets marins sur le littoral atlantique</t>
-  </si>
-  <si>
-    <t>Clean Atlantic, Union Européenne</t>
-  </si>
-  <si>
-    <t>Carqueiranne</t>
-  </si>
-  <si>
-    <t>Canet-en-Roussillon</t>
-  </si>
-  <si>
-    <t>La Londe-les-Maures</t>
-  </si>
-  <si>
-    <t>Emmanuelle</t>
-  </si>
-  <si>
-    <t>Structuration des données de suivi du Plan de Protection de l’Atmosphère de la zone urbaine de Nîmes</t>
-  </si>
-  <si>
-    <t>DREAL Occitanie</t>
-  </si>
-  <si>
-    <t>SIAO 13</t>
-  </si>
-  <si>
-    <t>Accès libre</t>
-  </si>
-  <si>
-    <t>n.c</t>
-  </si>
-  <si>
-    <t>Afficher Arnaud</t>
-  </si>
-  <si>
-    <t>Non</t>
-  </si>
-  <si>
-    <t>Analyse des déterminants du choix de résidence des ménages</t>
-  </si>
-  <si>
-    <t>Automatisation du baromètre de la coopération LEADER</t>
-  </si>
-  <si>
-    <t>Diagnostic de l’offre d’accompagnement de l’ESS</t>
-  </si>
-  <si>
-    <t>Diagnostic des déserts médicaux et modélisation de l’offre de téléconsultation</t>
-  </si>
-  <si>
-    <t>Application interactive dédiée à la lutte contre le désert médicaux</t>
-  </si>
-  <si>
-    <t>Diagnostic de la santé, la qualité de vie et du bien-être</t>
-  </si>
-  <si>
-    <t>Observatoire de la qualité de vie</t>
-  </si>
-  <si>
-    <t>Étude sur la mise en cohérence des fonctionnements du Services Intégré d'Accueil et d'Orientation (SIAO) avec les exigences du Logement d'Abord</t>
-  </si>
-  <si>
-    <t>ANCT - PETR Centre-Ouest Aveyron</t>
-  </si>
-  <si>
-    <t>Elaboration d’outils nationaux liés à la gouvernance et à la mise en œuvre des fonds européens</t>
-  </si>
-  <si>
-    <t>Etude d’impact du projet PISCOFAM</t>
-  </si>
-  <si>
-    <t>Analyse de la chaîne d’approvisionnement de la restauration collective et réalisation d’une application interactive collaborative</t>
-  </si>
-  <si>
-    <t>Mesure du potentiel de consommation en circuits courts</t>
-  </si>
-  <si>
-    <t>Prévision des effectifs scolaires</t>
+    <t>DDETS du Var</t>
+  </si>
+  <si>
+    <t>Logis-Cité</t>
   </si>
   <si>
     <t>Diagnostic auprès des jeunes sans abri dans le Var pour la DDETS du Var et le dispositif du SIAO</t>
+  </si>
+  <si>
+    <t>2023-2024</t>
+  </si>
+  <si>
+    <t>DDETS des Hautes-Alpes</t>
   </si>
   <si>
     <t>Logement social : Appui à la mise en conformité de
@@ -280,171 +403,57 @@
 des attributions</t>
   </si>
   <si>
+    <t>DREETS ARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accompagnement de la plateforme d’appui aux transitions professionnelles portée par la PAME 74 </t>
+  </si>
+  <si>
+    <t>CERC Ile de France</t>
+  </si>
+  <si>
     <t>Tableaux de bord emploi formation Bâtiment et Travaux publics région Ile de France</t>
   </si>
   <si>
+    <t>Département Allier</t>
+  </si>
+  <si>
+    <t>Mangove, Inkidata</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cartographie interactive pour l’accompagnement au diagnostic stratégique préalable d’un pacte local des solidarités dans le département de l’Allier </t>
   </si>
   <si>
+    <t>Métropole Montpellier et ses partenaires</t>
+  </si>
+  <si>
+    <t>CERC Occitanie</t>
+  </si>
+  <si>
     <t>Observatoire de l' Immobilier d'Entreprise de Montpellier et son territoire Urbain</t>
   </si>
   <si>
+    <t>2022, 2023, 2024 (en cours)</t>
+  </si>
+  <si>
     <t>Observatoire de l'Immobilier du Commerce Montpellier et son territoire Urbain</t>
   </si>
   <si>
-    <t>DDETS du Var</t>
-  </si>
-  <si>
-    <t>Terre d'Avance</t>
-  </si>
-  <si>
-    <t>CERC Ile de France</t>
-  </si>
-  <si>
-    <t>Département Allier</t>
-  </si>
-  <si>
-    <t>CERC Occitanie</t>
+    <t>Département des Alpes de Haute Provence</t>
   </si>
   <si>
     <t>Données de cadrage du plan départemental d'action pour le logement et l'hébergement des personnes défavorisées des Alpes de Hautes Provence</t>
   </si>
   <si>
-    <t>CEISS Consultants</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>Client final</t>
-  </si>
-  <si>
-    <t>Partenaires</t>
-  </si>
-  <si>
-    <t>TERRITEC</t>
-  </si>
-  <si>
-    <t>Logis-Cité</t>
-  </si>
-  <si>
-    <t>DDETS des Hautes-Alpes</t>
-  </si>
-  <si>
-    <t>Mangove, Inkidata</t>
-  </si>
-  <si>
-    <t>Métropole Montpellier et ses partenaires</t>
-  </si>
-  <si>
-    <t>Département des Alpes de Haute Provence</t>
-  </si>
-  <si>
-    <t>T_Bien-être territorial, santé et accès aux soins</t>
-  </si>
-  <si>
-    <t>T_Développement économique durable des territoires</t>
-  </si>
-  <si>
-    <t>T_Impact économique, social et environnemental</t>
-  </si>
-  <si>
-    <t>T_Mesure du potentiel sur les territoires</t>
-  </si>
-  <si>
-    <t>num</t>
+    <t>ARGE</t>
   </si>
   <si>
     <t>Etude socioéconomique de la pêche de loisir et de son potentiel de développement en Région Grand Est</t>
   </si>
   <si>
-    <t>2024 (en cours)</t>
-  </si>
-  <si>
-    <t>2022, 2023, 2024 (en cours)</t>
-  </si>
-  <si>
-    <t>ARGE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ministère de la Pêche et de l’Economie Maritime de Guinée - AFD </t>
-  </si>
-  <si>
-    <t>Novascopia</t>
-  </si>
-  <si>
-    <t>La Pitaya</t>
-  </si>
-  <si>
-    <t>Territoire &amp; Sens</t>
-  </si>
-  <si>
-    <t>Enalys</t>
-  </si>
-  <si>
-    <t>IRAM</t>
-  </si>
-  <si>
-    <t>Logis-Cité, Oxalys</t>
-  </si>
-  <si>
-    <t>Boréal</t>
-  </si>
-  <si>
-    <t>Expérience professionnelle au sein du cabinet AID Observatoire</t>
-  </si>
-  <si>
-    <t>Expérience professionnelle au sein du cabinet CRT Bretagne</t>
-  </si>
-  <si>
-    <t>terre d'Avance</t>
-  </si>
-  <si>
-    <t>Data Terra, Chrysalide</t>
-  </si>
-  <si>
-    <t>Teriteo</t>
-  </si>
-  <si>
-    <t>Cedre</t>
-  </si>
-  <si>
-    <t>Tero</t>
-  </si>
-  <si>
-    <t>Dowel Stratégie</t>
-  </si>
-  <si>
-    <t>CIVAM-LR</t>
-  </si>
-  <si>
-    <t>Expérience professionnelle au sein du Labex Entreprendre, Université de Montpellier</t>
-  </si>
-  <si>
-    <t>start_dates</t>
-  </si>
-  <si>
-    <t>end_dates</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
-    <t>Projets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accompagnement de la plateforme d’appui aux transitions professionnelles portée par la PAME 74 </t>
-  </si>
-  <si>
-    <t>DREETS ARA</t>
-  </si>
-  <si>
-    <t>selec</t>
-  </si>
-  <si>
     <t>FRBTP Guadeloupe</t>
   </si>
   <si>
@@ -457,36 +466,21 @@
     <t>Mission d'appui Observatoire territorialisé Habitat et Foncier</t>
   </si>
   <si>
-    <t>2023-2024</t>
+    <t>Région Bourgogne-Franche-Comte</t>
   </si>
   <si>
     <t>Aster Europe Conseil , Territeo</t>
   </si>
   <si>
-    <t>Région Bourgogne-Franche-Comte</t>
-  </si>
-  <si>
-    <t>T_Emploi/ Formation</t>
-  </si>
-  <si>
     <t>Modélisation et conseil pour la mise en place de vérifications de gestion ciblées sur les risques dans le cadre du pilotage des fonds européens</t>
   </si>
   <si>
-    <t>Veille et recherche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Désignation de la référence               </t>
-  </si>
-  <si>
     <t>beta gouv</t>
   </si>
   <si>
     <t xml:space="preserve">Data Analyst pour la mission InserJeunes de beta.gouv </t>
   </si>
   <si>
-    <t>Depuis 2023</t>
-  </si>
-  <si>
     <t>FFB Ocitanie</t>
   </si>
   <si>
@@ -496,21 +490,63 @@
     <t>Mission de structuration des indicateurs des Plans de Protection de l’Atmosphère de Montpellier, Nîmes et Toulouse</t>
   </si>
   <si>
-    <t>Fédération des CAE</t>
-  </si>
-  <si>
-    <t>Réalisation d'une étude d'impact socio-économique des CAE en France</t>
-  </si>
-  <si>
-    <t>2025 (en cours)</t>
+    <t>Statistiques des métiers de la filière FIBOIS en Auvergne Rhônes-Alpes</t>
+  </si>
+  <si>
+    <t>CA Gaillac-Graulhet</t>
+  </si>
+  <si>
+    <t>Logis-Cité, AteliersUp+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Données de cadrage pour étude urbaine pré-opérationnelle Commune de Briatexte </t>
+  </si>
+  <si>
+    <t>Terre d'Avance, Enalys</t>
+  </si>
+  <si>
+    <t>Fédération Nationale de la Pêche en France (FNFP)</t>
+  </si>
+  <si>
+    <t>Etude socioéconomique de la pêche de loisir et de son potentiel de développement au niveau national (en cours)</t>
+  </si>
+  <si>
+    <t>Commentaire</t>
+  </si>
+  <si>
+    <t>CIRAD</t>
+  </si>
+  <si>
+    <t>Outil d'appui à l'exploration d'une base de données d'indicateurs de 22 pays du Pacifique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maquettage et mise en forme graphique d’un rappor –Indicateurs clés de la
+transition énergétique des bâtiments </t>
+  </si>
+  <si>
+    <t>Optimisation d’un outil de projections macro-économiques par métier à moyen terme : mise à jour données d'input</t>
+  </si>
+  <si>
+    <t>2023-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production d’outils numériques et dataviz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expertise des données socio-économique et des territoires </t>
+  </si>
+  <si>
+    <t>Pilotage et suivi dans le temps</t>
+  </si>
+  <si>
+    <t>Formation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;€&quot;;[Red]\-#,##0\ &quot;€&quot;"/>
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;??\ &quot;€&quot;_-;_-@_-"/>
   </numFmts>
@@ -565,7 +601,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -573,7 +609,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Monétaire" xfId="1" builtinId="4"/>
@@ -889,92 +924,108 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B3B7FE-E50F-4A1F-B29E-52CC043F3381}">
-  <dimension ref="A1:T50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:Y55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="3" width="22.59765625" customWidth="1"/>
     <col min="4" max="4" width="71" customWidth="1"/>
-    <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="11.86328125" customWidth="1"/>
+    <col min="8" max="16" width="11.3984375" customWidth="1"/>
     <col min="17" max="17" width="14.73046875" customWidth="1"/>
     <col min="18" max="18" width="14.1328125" customWidth="1"/>
+    <col min="19" max="21" width="11.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="21" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:25" ht="21" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>92</v>
+        <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>103</v>
+        <v>5</v>
       </c>
       <c r="G1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>55</v>
+        <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>61</v>
+        <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>141</v>
+        <v>12</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>101</v>
+        <v>13</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>102</v>
+        <v>14</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>143</v>
+        <v>15</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>126</v>
+        <v>16</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>127</v>
+        <v>17</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="Y1" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>109</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="E2">
         <v>2017</v>
@@ -987,27 +1038,36 @@
         <v>14000</v>
       </c>
       <c r="H2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J2" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="K2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V2" t="s">
+        <v>25</v>
+      </c>
+      <c r="W2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>28</v>
       </c>
       <c r="E3">
         <v>2017</v>
@@ -1020,27 +1080,36 @@
         <v>12000</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="K3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V3" t="s">
+        <v>25</v>
+      </c>
+      <c r="W3" t="s">
+        <v>25</v>
+      </c>
+      <c r="X3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B4" t="s">
         <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4">
         <v>2020</v>
@@ -1053,27 +1122,33 @@
         <v>7550</v>
       </c>
       <c r="H4" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J4" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="K4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V4" t="s">
+        <v>25</v>
+      </c>
+      <c r="X4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E5">
         <v>2021</v>
@@ -1086,27 +1161,33 @@
         <v>2250</v>
       </c>
       <c r="H5" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J5" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="K5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V5" t="s">
+        <v>25</v>
+      </c>
+      <c r="W5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
         <v>37</v>
       </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>89</v>
-      </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E6">
         <v>2021</v>
@@ -1119,27 +1200,33 @@
         <v>4500</v>
       </c>
       <c r="H6" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J6" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="K6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V6" t="s">
+        <v>25</v>
+      </c>
+      <c r="W6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="E7">
         <v>2021</v>
@@ -1152,27 +1239,30 @@
         <v>1470</v>
       </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J7" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="K7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" t="s">
         <v>37</v>
       </c>
-      <c r="B8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" t="s">
-        <v>89</v>
-      </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E8">
         <v>2022</v>
@@ -1185,27 +1275,33 @@
         <v>4500</v>
       </c>
       <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" t="s">
+        <v>25</v>
+      </c>
+      <c r="V8" t="s">
+        <v>25</v>
+      </c>
+      <c r="W8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
         <v>42</v>
       </c>
-      <c r="J8" t="s">
-        <v>62</v>
-      </c>
-      <c r="K8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
       <c r="D9" t="s">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F9">
         <v>2020</v>
@@ -1214,30 +1310,36 @@
         <v>5000</v>
       </c>
       <c r="H9" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
+      </c>
+      <c r="V9" t="s">
+        <v>25</v>
+      </c>
+      <c r="W9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
         <v>42</v>
       </c>
-      <c r="J9" t="s">
-        <v>62</v>
-      </c>
-      <c r="K9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
       <c r="D10" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F10">
         <v>2023</v>
@@ -1246,27 +1348,33 @@
         <v>22000</v>
       </c>
       <c r="H10" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J10" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="K10" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V10" t="s">
+        <v>25</v>
+      </c>
+      <c r="W10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="C11" t="s">
-        <v>113</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="E11">
         <v>2016</v>
@@ -1279,30 +1387,33 @@
         <v>6250</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J11" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L11" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="T11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W11" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>2</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E12">
         <v>2018</v>
@@ -1315,27 +1426,36 @@
         <v>8000</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J12" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L12" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V12" t="s">
+        <v>25</v>
+      </c>
+      <c r="W12" t="s">
+        <v>25</v>
+      </c>
+      <c r="X12" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E13">
         <v>2019</v>
@@ -1348,30 +1468,36 @@
         <v>5000</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J13" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L13" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="T13" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V13" t="s">
+        <v>25</v>
+      </c>
+      <c r="W13" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E14">
         <v>2021</v>
@@ -1384,27 +1510,30 @@
         <v>1875</v>
       </c>
       <c r="H14" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J14" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L14" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="E15">
         <v>2022</v>
@@ -1417,27 +1546,36 @@
         <v>5250</v>
       </c>
       <c r="H15" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J15" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V15" t="s">
+        <v>25</v>
+      </c>
+      <c r="W15" t="s">
+        <v>25</v>
+      </c>
+      <c r="X15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E16">
         <v>2023</v>
@@ -1450,53 +1588,62 @@
         <v>99610</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J16" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L16" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W16" t="s">
+        <v>25</v>
+      </c>
+      <c r="X16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>64</v>
       </c>
       <c r="D17" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="F17">
         <v>2010</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H17" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J17" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L17" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="E18">
         <v>2011</v>
@@ -1506,30 +1653,36 @@
         <v>2011</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H18" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J18" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="N18" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W18" t="s">
+        <v>25</v>
+      </c>
+      <c r="X18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="E19">
         <v>2017</v>
@@ -1542,30 +1695,33 @@
         <v>6400</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J19" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="N19" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="T19" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="E20">
         <v>2018</v>
@@ -1578,30 +1734,33 @@
         <v>10000</v>
       </c>
       <c r="H20" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J20" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="N20" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="T20" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="D21" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="E21">
         <v>2020</v>
@@ -1614,27 +1773,30 @@
         <v>17640</v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J21" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="N21" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="E22">
         <v>2021</v>
@@ -1647,27 +1809,33 @@
         <v>14000</v>
       </c>
       <c r="H22" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J22" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="N22" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W22" t="s">
+        <v>25</v>
+      </c>
+      <c r="X22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="E23">
         <v>2021</v>
@@ -1680,27 +1848,33 @@
         <v>3660</v>
       </c>
       <c r="H23" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J23" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="N23" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V23" t="s">
+        <v>25</v>
+      </c>
+      <c r="W23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="E24">
         <v>2022</v>
@@ -1713,30 +1887,36 @@
         <v>2250</v>
       </c>
       <c r="H24" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J24" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="N24" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="T24" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W24" t="s">
+        <v>25</v>
+      </c>
+      <c r="X24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="E25">
         <v>2022</v>
@@ -1749,27 +1929,30 @@
         <v>20000</v>
       </c>
       <c r="H25" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J25" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="N25" t="s">
+        <v>25</v>
+      </c>
+      <c r="W25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" t="s">
-        <v>108</v>
-      </c>
-      <c r="C26" t="s">
-        <v>122</v>
-      </c>
-      <c r="D26" t="s">
-        <v>73</v>
       </c>
       <c r="E26">
         <v>2023</v>
@@ -1782,24 +1965,27 @@
         <v>18000</v>
       </c>
       <c r="H26" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J26" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="N26" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="E27">
         <v>2023</v>
@@ -1812,16 +1998,16 @@
         <v>26400</v>
       </c>
       <c r="H27" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="I27" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J27" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="N27" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="Q27" s="4">
         <v>44887</v>
@@ -1830,24 +2016,33 @@
         <v>45260</v>
       </c>
       <c r="S27" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.45">
+        <v>93</v>
+      </c>
+      <c r="V27" t="s">
+        <v>25</v>
+      </c>
+      <c r="W27" t="s">
+        <v>25</v>
+      </c>
+      <c r="X27" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D28" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="F28">
         <v>2023</v>
@@ -1856,19 +2051,16 @@
         <v>58875</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="I28" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J28" t="s">
-        <v>42</v>
-      </c>
-      <c r="M28" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="N28" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="Q28" s="4">
         <v>45261</v>
@@ -1877,21 +2069,33 @@
         <v>45291</v>
       </c>
       <c r="S28" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="T28" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V28" t="s">
+        <v>25</v>
+      </c>
+      <c r="W28" t="s">
+        <v>25</v>
+      </c>
+      <c r="X28" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B29" t="s">
-        <v>23</v>
+        <v>98</v>
       </c>
       <c r="D29" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="E29">
         <v>2016</v>
@@ -1901,30 +2105,36 @@
         <v>2016</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J29" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="O29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V29" t="s">
+        <v>25</v>
+      </c>
+      <c r="W29" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="D30" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="E30">
         <v>2016</v>
@@ -1937,27 +2147,30 @@
         <v>6400</v>
       </c>
       <c r="H30" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J30" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="O30" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W30" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B31" t="s">
-        <v>20</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="D31" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E31">
         <v>2017</v>
@@ -1970,24 +2183,30 @@
         <v>2500</v>
       </c>
       <c r="H31" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J31" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="O31" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V31" t="s">
+        <v>25</v>
+      </c>
+      <c r="W31" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="E32">
         <v>2018</v>
@@ -2000,24 +2219,30 @@
         <v>10000</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J32" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="O32" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V32" t="s">
+        <v>25</v>
+      </c>
+      <c r="W32" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="D33" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="E33">
         <v>2022</v>
@@ -2030,24 +2255,27 @@
         <v>6375</v>
       </c>
       <c r="H33" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J33" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="O33" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>41</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="D34" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="E34">
         <v>2014</v>
@@ -2057,33 +2285,39 @@
         <v>2014</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="H34" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J34" t="s">
-        <v>42</v>
+        <v>24</v>
+      </c>
+      <c r="O34" t="s">
+        <v>25</v>
       </c>
       <c r="P34" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W34" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D35" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="E35" t="s">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="F35">
         <v>20241</v>
@@ -2092,24 +2326,27 @@
         <v>5075</v>
       </c>
       <c r="I35" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="K35" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" ht="42.75" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W35" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B36" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="C36" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="E36">
         <v>2023</v>
@@ -2122,24 +2359,27 @@
         <v>4400</v>
       </c>
       <c r="I36" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="N36" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W36" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="D37" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="E37">
         <v>2022</v>
@@ -2152,27 +2392,30 @@
         <v>7000</v>
       </c>
       <c r="I37" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L37" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="M37" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="T37" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W37" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="D38" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="E38">
         <v>2023</v>
@@ -2185,30 +2428,36 @@
         <v>13200</v>
       </c>
       <c r="I38" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L38" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="M38" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="T38" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V38" t="s">
+        <v>25</v>
+      </c>
+      <c r="W38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="C39" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="D39" t="s">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="E39">
         <v>2023</v>
@@ -2221,27 +2470,30 @@
         <v>3400</v>
       </c>
       <c r="I39" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L39" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="V39" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C40" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="D40" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="E40" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="F40">
         <v>20243</v>
@@ -2251,24 +2503,30 @@
         <v>12600</v>
       </c>
       <c r="I40" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L40" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W40" t="s">
+        <v>25</v>
+      </c>
+      <c r="X40" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C41" t="s">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="D41" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="E41">
         <v>2022</v>
@@ -2281,24 +2539,30 @@
         <v>6300</v>
       </c>
       <c r="I41" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L41" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W41" t="s">
+        <v>25</v>
+      </c>
+      <c r="X41" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" t="s">
         <v>37</v>
       </c>
-      <c r="B42" t="s">
-        <v>98</v>
-      </c>
-      <c r="C42" t="s">
-        <v>89</v>
-      </c>
       <c r="D42" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="E42">
         <v>2022</v>
@@ -2311,24 +2575,27 @@
         <v>3570</v>
       </c>
       <c r="I42" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L42" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.45">
+        <v>25</v>
+      </c>
+      <c r="W42" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B43" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="C43" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="E43">
         <v>2024</v>
@@ -2340,22 +2607,22 @@
         <v>48400</v>
       </c>
       <c r="H43" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="I43" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J43" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L43" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="N43" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="O43" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="Q43" s="4">
         <v>45310</v>
@@ -2364,24 +2631,27 @@
         <v>45657</v>
       </c>
       <c r="S43" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.45">
+        <v>136</v>
+      </c>
+      <c r="W43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B44" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>135</v>
-      </c>
-      <c r="E44" t="s">
-        <v>105</v>
+        <v>138</v>
+      </c>
+      <c r="E44">
+        <v>2024</v>
       </c>
       <c r="F44">
         <v>20244</v>
@@ -2390,13 +2660,13 @@
         <v>9750</v>
       </c>
       <c r="I44" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L44" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="M44" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="Q44" s="4">
         <v>45323</v>
@@ -2405,18 +2675,21 @@
         <v>45627</v>
       </c>
       <c r="S44" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.45">
+        <v>136</v>
+      </c>
+      <c r="W44" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B45" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D45" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E45">
         <v>2024</v>
@@ -2429,16 +2702,16 @@
         <v>16000</v>
       </c>
       <c r="I45" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L45" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="N45" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="O45" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="Q45" s="4">
         <v>45323</v>
@@ -2446,19 +2719,25 @@
       <c r="R45" s="4">
         <v>45473</v>
       </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="W45" t="s">
+        <v>25</v>
+      </c>
+      <c r="X45" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B46" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C46" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D46" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E46">
         <v>2024</v>
@@ -2470,19 +2749,19 @@
         <v>17213</v>
       </c>
       <c r="H46" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="I46" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J46" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="L46" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="O46" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="Q46" s="4">
         <v>45323</v>
@@ -2490,48 +2769,63 @@
       <c r="R46" s="4">
         <v>45566</v>
       </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="W46" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B47" t="s">
+        <v>144</v>
+      </c>
+      <c r="D47" t="s">
         <v>145</v>
       </c>
-      <c r="D47" t="s">
-        <v>146</v>
-      </c>
       <c r="E47" t="s">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="F47">
         <v>2023</v>
       </c>
       <c r="G47" s="1">
-        <v>85000</v>
+        <v>184000</v>
       </c>
       <c r="H47" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="J47" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="M47" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="Q47" s="4">
         <v>45108</v>
       </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="R47" s="4">
+        <v>46053</v>
+      </c>
+      <c r="V47" t="s">
+        <v>25</v>
+      </c>
+      <c r="W47" t="s">
+        <v>25</v>
+      </c>
+      <c r="X47" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="D48" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E48">
         <v>2024</v>
@@ -2544,10 +2838,10 @@
         <v>8000</v>
       </c>
       <c r="I48" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="O48" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="Q48" s="4">
         <v>45566</v>
@@ -2555,16 +2849,22 @@
       <c r="R48" s="4">
         <v>45657</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="V48" t="s">
+        <v>25</v>
+      </c>
+      <c r="W48" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="D49" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E49">
         <v>2024</v>
@@ -2576,13 +2876,13 @@
         <v>16200</v>
       </c>
       <c r="I49" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="N49" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="O49" t="s">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="Q49" s="4">
         <v>45536</v>
@@ -2590,47 +2890,238 @@
       <c r="R49" s="4">
         <v>45657</v>
       </c>
-    </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="V49" t="s">
+        <v>25</v>
+      </c>
+      <c r="W49" t="s">
+        <v>25</v>
+      </c>
+      <c r="X49" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B50" t="s">
+        <v>27</v>
+      </c>
+      <c r="D50" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50">
+        <v>2025</v>
+      </c>
+      <c r="F50">
+        <v>20249</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1700</v>
+      </c>
+      <c r="I50" t="s">
+        <v>24</v>
+      </c>
+      <c r="M50" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q50" s="4">
+        <v>45689</v>
+      </c>
+      <c r="R50" s="4">
+        <v>45703</v>
+      </c>
+      <c r="W50" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" t="s">
         <v>151</v>
       </c>
-      <c r="C50" t="s">
-        <v>111</v>
-      </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>152</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E51">
+        <v>2025</v>
+      </c>
+      <c r="F51">
+        <v>2025</v>
+      </c>
+      <c r="G51" s="1">
+        <f>2.5*750</f>
+        <v>1875</v>
+      </c>
+      <c r="I51" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>45690</v>
+      </c>
+      <c r="R51" s="4">
+        <v>45746</v>
+      </c>
+      <c r="W51" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>20</v>
+      </c>
+      <c r="B52" t="s">
+        <v>154</v>
+      </c>
+      <c r="C52" t="s">
         <v>153</v>
       </c>
-      <c r="F50">
-        <v>20251</v>
-      </c>
-      <c r="G50" s="5">
-        <v>82500</v>
-      </c>
-      <c r="H50" t="s">
-        <v>42</v>
-      </c>
-      <c r="J50" t="s">
-        <v>42</v>
-      </c>
-      <c r="L50" t="s">
-        <v>90</v>
-      </c>
-      <c r="N50" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q50" s="4">
-        <v>45731</v>
+      <c r="D52" t="s">
+        <v>155</v>
+      </c>
+      <c r="E52">
+        <v>2025</v>
+      </c>
+      <c r="F52">
+        <v>2025</v>
+      </c>
+      <c r="G52" s="1">
+        <v>24000</v>
+      </c>
+      <c r="H52" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" t="s">
+        <v>24</v>
+      </c>
+      <c r="N52" t="s">
+        <v>25</v>
+      </c>
+      <c r="O52" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q52" s="4">
+        <v>45718</v>
+      </c>
+      <c r="V52" t="s">
+        <v>25</v>
+      </c>
+      <c r="W52" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>20</v>
+      </c>
+      <c r="B53" t="s">
+        <v>157</v>
+      </c>
+      <c r="D53" t="s">
+        <v>158</v>
+      </c>
+      <c r="E53">
+        <v>2025</v>
+      </c>
+      <c r="F53">
+        <v>2025</v>
+      </c>
+      <c r="G53" s="1">
+        <v>4250</v>
+      </c>
+      <c r="I53" t="s">
+        <v>24</v>
+      </c>
+      <c r="O53" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q53" s="4">
+        <v>45901</v>
+      </c>
+      <c r="R53" s="4">
+        <v>46022</v>
+      </c>
+      <c r="V53" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>20</v>
+      </c>
+      <c r="B54" t="s">
+        <v>122</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E54">
+        <v>2025</v>
+      </c>
+      <c r="F54">
+        <v>2025</v>
+      </c>
+      <c r="G54" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I54" t="s">
+        <v>24</v>
+      </c>
+      <c r="M54" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q54" s="4">
+        <v>45901</v>
+      </c>
+      <c r="R54" s="4">
+        <v>46022</v>
+      </c>
+      <c r="V54" t="s">
+        <v>25</v>
+      </c>
+      <c r="W54" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>20</v>
+      </c>
+      <c r="B55" t="s">
+        <v>94</v>
+      </c>
+      <c r="D55" t="s">
+        <v>160</v>
+      </c>
+      <c r="E55">
+        <v>2025</v>
+      </c>
+      <c r="F55">
+        <v>2025</v>
+      </c>
+      <c r="G55" s="1">
+        <f>850*3.5</f>
+        <v>2975</v>
+      </c>
+      <c r="I55" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q55" s="4">
+        <v>45931</v>
+      </c>
+      <c r="R55" s="4">
+        <v>46052</v>
+      </c>
+      <c r="W55" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T49" xr:uid="{D9B3B7FE-E50F-4A1F-B29E-52CC043F3381}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I34">
     <sortCondition ref="E2:E34"/>
   </sortState>

--- a/site-dsidd/docs/references/references_dsidd_v2.xlsx
+++ b/site-dsidd/docs/references/references_dsidd_v2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arnau\d-sidd Dropbox\Equipe\sites internet\Site rmarkdown\site-dsidd\references\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCCAA659-A2B9-4008-A52D-D5C751BE3B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE56C90A-629C-463D-8642-874596701DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8A1639DB-56E8-489A-8363-79F7F85173AB}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$T$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Feuil1!$A$1:$W$59</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="174">
   <si>
     <t>Origine expérience</t>
   </si>
@@ -71,22 +71,7 @@
     <t>Afficher Arnaud</t>
   </si>
   <si>
-    <t>T_Bien-être territorial, santé et accès aux soins</t>
-  </si>
-  <si>
-    <t>T_Développement économique durable des territoires</t>
-  </si>
-  <si>
     <t>T_Emploi/ Formation</t>
-  </si>
-  <si>
-    <t>T_Impact économique, social et environnemental</t>
-  </si>
-  <si>
-    <t>T_Mesure du potentiel sur les territoires</t>
-  </si>
-  <si>
-    <t>Veille et recherche</t>
   </si>
   <si>
     <t>start_dates</t>
@@ -540,6 +525,45 @@
   </si>
   <si>
     <t>Formation</t>
+  </si>
+  <si>
+    <t>CRT Bretagne</t>
+  </si>
+  <si>
+    <t>Multiple</t>
+  </si>
+  <si>
+    <t>Confédération générale des SCOP</t>
+  </si>
+  <si>
+    <t>Impact socio-économique des CAE en France</t>
+  </si>
+  <si>
+    <t>Teritéo</t>
+  </si>
+  <si>
+    <t>DGEFP</t>
+  </si>
+  <si>
+    <t>Ministère de l'Agriculture et de la Souveraineté Alimentaire</t>
+  </si>
+  <si>
+    <t>Evaluation Plan Stratégiques National (PSN) de la Politique Agricole Commune (PAC) 2023-2027</t>
+  </si>
+  <si>
+    <t>Evaluation des parcours des participants du Fonds social européen (FSE et FSE+)</t>
+  </si>
+  <si>
+    <t>Baromètre appui à la coopération des GAL LEADER (ACGL)</t>
+  </si>
+  <si>
+    <t>T_Santé globale des territoires</t>
+  </si>
+  <si>
+    <t>T_Développement économique et social</t>
+  </si>
+  <si>
+    <t>T_Mesure d'impact &amp; modélisation</t>
   </si>
 </sst>
 </file>
@@ -924,20 +948,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B3B7FE-E50F-4A1F-B29E-52CC043F3381}">
-  <dimension ref="A1:Y55"/>
+  <dimension ref="A1:W59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="3" width="22.59765625" customWidth="1"/>
     <col min="4" max="4" width="71" customWidth="1"/>
     <col min="5" max="6" width="18" customWidth="1"/>
     <col min="7" max="7" width="11.86328125" customWidth="1"/>
-    <col min="8" max="16" width="11.3984375" customWidth="1"/>
-    <col min="17" max="17" width="14.73046875" customWidth="1"/>
-    <col min="18" max="18" width="14.1328125" customWidth="1"/>
-    <col min="19" max="21" width="11.3984375" customWidth="1"/>
+    <col min="8" max="14" width="11.3984375" customWidth="1"/>
+    <col min="15" max="15" width="14.73046875" customWidth="1"/>
+    <col min="16" max="16" width="14.1328125" customWidth="1"/>
+    <col min="17" max="19" width="11.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="21" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:23" ht="21" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -969,63 +993,57 @@
         <v>9</v>
       </c>
       <c r="K1" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="O1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="D2" t="s">
         <v>18</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
       </c>
       <c r="E2">
         <v>2017</v>
@@ -1038,36 +1056,36 @@
         <v>14000</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="T2" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" t="s">
+        <v>20</v>
       </c>
       <c r="V2" t="s">
-        <v>25</v>
-      </c>
-      <c r="W2" t="s">
-        <v>25</v>
-      </c>
-      <c r="X2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <v>2017</v>
@@ -1080,36 +1098,36 @@
         <v>12000</v>
       </c>
       <c r="H3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T3" t="s">
+        <v>20</v>
+      </c>
+      <c r="U3" t="s">
+        <v>20</v>
+      </c>
+      <c r="V3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="V3" t="s">
-        <v>25</v>
-      </c>
-      <c r="W3" t="s">
-        <v>25</v>
-      </c>
-      <c r="X3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>30</v>
-      </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E4">
         <v>2020</v>
@@ -1122,33 +1140,33 @@
         <v>7550</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="T4" t="s">
+        <v>20</v>
       </c>
       <c r="V4" t="s">
-        <v>25</v>
-      </c>
-      <c r="X4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E5">
         <v>2021</v>
@@ -1161,33 +1179,33 @@
         <v>2250</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="V5" t="s">
-        <v>25</v>
-      </c>
-      <c r="W5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="T5" t="s">
+        <v>20</v>
+      </c>
+      <c r="U5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E6">
         <v>2021</v>
@@ -1200,33 +1218,33 @@
         <v>4500</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" t="s">
+        <v>20</v>
+      </c>
+      <c r="T6" t="s">
+        <v>20</v>
+      </c>
+      <c r="U6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
         <v>35</v>
-      </c>
-      <c r="K6" t="s">
-        <v>25</v>
-      </c>
-      <c r="V6" t="s">
-        <v>25</v>
-      </c>
-      <c r="W6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>40</v>
       </c>
       <c r="E7">
         <v>2021</v>
@@ -1239,30 +1257,30 @@
         <v>1470</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K7" t="s">
-        <v>25</v>
-      </c>
-      <c r="V7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="T7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E8">
         <v>2022</v>
@@ -1275,33 +1293,33 @@
         <v>4500</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J8" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K8" t="s">
-        <v>25</v>
-      </c>
-      <c r="V8" t="s">
-        <v>25</v>
-      </c>
-      <c r="W8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="T8" t="s">
+        <v>20</v>
+      </c>
+      <c r="U8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E9" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F9">
         <v>2020</v>
@@ -1310,36 +1328,36 @@
         <v>5000</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J9" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K9" t="s">
-        <v>25</v>
-      </c>
-      <c r="V9" t="s">
-        <v>25</v>
-      </c>
-      <c r="W9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="T9" t="s">
+        <v>20</v>
+      </c>
+      <c r="U9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" t="s">
         <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" t="s">
-        <v>47</v>
       </c>
       <c r="F10">
         <v>2023</v>
@@ -1348,33 +1366,33 @@
         <v>22000</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J10" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K10" t="s">
-        <v>25</v>
-      </c>
-      <c r="V10" t="s">
-        <v>25</v>
-      </c>
-      <c r="W10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="T10" t="s">
+        <v>20</v>
+      </c>
+      <c r="U10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E11">
         <v>2016</v>
@@ -1387,33 +1405,33 @@
         <v>6250</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J11" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L11" t="s">
-        <v>25</v>
-      </c>
-      <c r="T11" t="s">
-        <v>25</v>
-      </c>
-      <c r="W11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="R11" t="s">
+        <v>20</v>
+      </c>
+      <c r="U11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D12" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="E12">
         <v>2018</v>
@@ -1426,36 +1444,36 @@
         <v>8000</v>
       </c>
       <c r="H12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L12" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="T12" t="s">
+        <v>20</v>
+      </c>
+      <c r="U12" t="s">
+        <v>20</v>
       </c>
       <c r="V12" t="s">
-        <v>25</v>
-      </c>
-      <c r="W12" t="s">
-        <v>25</v>
-      </c>
-      <c r="X12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E13">
         <v>2019</v>
@@ -1468,36 +1486,36 @@
         <v>5000</v>
       </c>
       <c r="H13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L13" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="R13" t="s">
+        <v>20</v>
       </c>
       <c r="T13" t="s">
-        <v>25</v>
-      </c>
-      <c r="V13" t="s">
-        <v>25</v>
-      </c>
-      <c r="W13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U13" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="E14">
         <v>2021</v>
@@ -1510,30 +1528,30 @@
         <v>1875</v>
       </c>
       <c r="H14" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L14" t="s">
-        <v>25</v>
-      </c>
-      <c r="V14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="T14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E15">
         <v>2022</v>
@@ -1546,36 +1564,36 @@
         <v>5250</v>
       </c>
       <c r="H15" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J15" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L15" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="T15" t="s">
+        <v>20</v>
+      </c>
+      <c r="U15" t="s">
+        <v>20</v>
       </c>
       <c r="V15" t="s">
-        <v>25</v>
-      </c>
-      <c r="W15" t="s">
-        <v>25</v>
-      </c>
-      <c r="X15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E16">
         <v>2023</v>
@@ -1588,62 +1606,68 @@
         <v>99610</v>
       </c>
       <c r="H16" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J16" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L16" t="s">
-        <v>25</v>
-      </c>
-      <c r="W16" t="s">
-        <v>25</v>
-      </c>
-      <c r="X16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U16" t="s">
+        <v>20</v>
+      </c>
+      <c r="V16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>63</v>
+        <v>58</v>
+      </c>
+      <c r="B17" t="s">
+        <v>162</v>
       </c>
       <c r="C17" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F17">
         <v>2010</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H17" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J17" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L17" t="s">
-        <v>25</v>
-      </c>
-      <c r="W17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>161</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E18">
         <v>2011</v>
@@ -1653,36 +1677,36 @@
         <v>2011</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J18" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N18" t="s">
-        <v>25</v>
-      </c>
-      <c r="W18" t="s">
-        <v>25</v>
-      </c>
-      <c r="X18" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U18" t="s">
+        <v>20</v>
+      </c>
+      <c r="V18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E19">
         <v>2017</v>
@@ -1695,33 +1719,33 @@
         <v>6400</v>
       </c>
       <c r="H19" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J19" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N19" t="s">
-        <v>25</v>
-      </c>
-      <c r="T19" t="s">
-        <v>25</v>
-      </c>
-      <c r="W19" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="R19" t="s">
+        <v>20</v>
+      </c>
+      <c r="U19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="E20">
         <v>2018</v>
@@ -1734,33 +1758,33 @@
         <v>10000</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N20" t="s">
-        <v>25</v>
-      </c>
-      <c r="T20" t="s">
-        <v>25</v>
-      </c>
-      <c r="W20" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="R20" t="s">
+        <v>20</v>
+      </c>
+      <c r="U20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E21">
         <v>2020</v>
@@ -1773,30 +1797,30 @@
         <v>17640</v>
       </c>
       <c r="H21" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J21" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="N21" t="s">
-        <v>25</v>
-      </c>
-      <c r="W21" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U21" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D22" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E22">
         <v>2021</v>
@@ -1809,33 +1833,33 @@
         <v>14000</v>
       </c>
       <c r="H22" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J22" t="s">
-        <v>24</v>
-      </c>
-      <c r="N22" t="s">
-        <v>25</v>
-      </c>
-      <c r="W22" t="s">
-        <v>25</v>
-      </c>
-      <c r="X22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+      <c r="L22" t="s">
+        <v>20</v>
+      </c>
+      <c r="U22" t="s">
+        <v>20</v>
+      </c>
+      <c r="V22" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C23" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E23">
         <v>2021</v>
@@ -1848,33 +1872,33 @@
         <v>3660</v>
       </c>
       <c r="H23" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J23" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N23" t="s">
-        <v>25</v>
-      </c>
-      <c r="V23" t="s">
-        <v>25</v>
-      </c>
-      <c r="W23" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="T23" t="s">
+        <v>20</v>
+      </c>
+      <c r="U23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E24">
         <v>2022</v>
@@ -1887,36 +1911,36 @@
         <v>2250</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J24" t="s">
-        <v>24</v>
-      </c>
-      <c r="N24" t="s">
-        <v>25</v>
-      </c>
-      <c r="T24" t="s">
-        <v>25</v>
-      </c>
-      <c r="W24" t="s">
-        <v>25</v>
-      </c>
-      <c r="X24" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+      <c r="L24" t="s">
+        <v>20</v>
+      </c>
+      <c r="R24" t="s">
+        <v>20</v>
+      </c>
+      <c r="U24" t="s">
+        <v>20</v>
+      </c>
+      <c r="V24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="E25">
         <v>2022</v>
@@ -1929,30 +1953,30 @@
         <v>20000</v>
       </c>
       <c r="H25" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J25" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N25" t="s">
-        <v>25</v>
-      </c>
-      <c r="W25" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U25" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C26" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E26">
         <v>2023</v>
@@ -1965,27 +1989,27 @@
         <v>18000</v>
       </c>
       <c r="H26" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J26" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N26" t="s">
-        <v>25</v>
-      </c>
-      <c r="W26" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="E27">
         <v>2023</v>
@@ -1998,51 +2022,51 @@
         <v>26400</v>
       </c>
       <c r="H27" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I27" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J27" t="s">
-        <v>24</v>
-      </c>
-      <c r="N27" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q27" s="4">
+        <v>19</v>
+      </c>
+      <c r="K27" t="s">
+        <v>20</v>
+      </c>
+      <c r="O27" s="4">
         <v>44887</v>
       </c>
-      <c r="R27" s="4">
+      <c r="P27" s="4">
         <v>45260</v>
       </c>
-      <c r="S27" t="s">
-        <v>93</v>
+      <c r="Q27" t="s">
+        <v>88</v>
+      </c>
+      <c r="T27" t="s">
+        <v>20</v>
+      </c>
+      <c r="U27" t="s">
+        <v>20</v>
       </c>
       <c r="V27" t="s">
-        <v>25</v>
-      </c>
-      <c r="W27" t="s">
-        <v>25</v>
-      </c>
-      <c r="X27" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F28">
         <v>2023</v>
@@ -2051,51 +2075,51 @@
         <v>58875</v>
       </c>
       <c r="H28" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I28" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J28" t="s">
-        <v>24</v>
-      </c>
-      <c r="N28" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q28" s="4">
+        <v>19</v>
+      </c>
+      <c r="M28" t="s">
+        <v>20</v>
+      </c>
+      <c r="O28" s="4">
         <v>45261</v>
       </c>
-      <c r="R28" s="4">
+      <c r="P28" s="4">
         <v>45291</v>
       </c>
-      <c r="S28" t="s">
+      <c r="Q28" t="s">
+        <v>88</v>
+      </c>
+      <c r="R28" t="s">
+        <v>20</v>
+      </c>
+      <c r="T28" t="s">
+        <v>20</v>
+      </c>
+      <c r="U28" t="s">
+        <v>20</v>
+      </c>
+      <c r="V28" t="s">
+        <v>20</v>
+      </c>
+      <c r="W28" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
         <v>93</v>
       </c>
-      <c r="T28" t="s">
-        <v>25</v>
-      </c>
-      <c r="V28" t="s">
-        <v>25</v>
-      </c>
-      <c r="W28" t="s">
-        <v>25</v>
-      </c>
-      <c r="X28" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" t="s">
-        <v>98</v>
-      </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E29">
         <v>2016</v>
@@ -2105,36 +2129,36 @@
         <v>2016</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="H29" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J29" t="s">
-        <v>24</v>
-      </c>
-      <c r="O29" t="s">
-        <v>25</v>
-      </c>
-      <c r="V29" t="s">
-        <v>25</v>
-      </c>
-      <c r="W29" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+      <c r="K29" t="s">
+        <v>20</v>
+      </c>
+      <c r="T29" t="s">
+        <v>20</v>
+      </c>
+      <c r="U29" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D30" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E30">
         <v>2016</v>
@@ -2147,30 +2171,30 @@
         <v>6400</v>
       </c>
       <c r="H30" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J30" t="s">
-        <v>24</v>
-      </c>
-      <c r="O30" t="s">
-        <v>25</v>
-      </c>
-      <c r="W30" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+      <c r="N30" t="s">
+        <v>20</v>
+      </c>
+      <c r="U30" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C31" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E31">
         <v>2017</v>
@@ -2183,30 +2207,30 @@
         <v>2500</v>
       </c>
       <c r="H31" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J31" t="s">
-        <v>24</v>
-      </c>
-      <c r="O31" t="s">
-        <v>25</v>
-      </c>
-      <c r="V31" t="s">
-        <v>25</v>
-      </c>
-      <c r="W31" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+      <c r="K31" t="s">
+        <v>20</v>
+      </c>
+      <c r="T31" t="s">
+        <v>20</v>
+      </c>
+      <c r="U31" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E32">
         <v>2018</v>
@@ -2219,30 +2243,30 @@
         <v>10000</v>
       </c>
       <c r="H32" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J32" t="s">
-        <v>24</v>
-      </c>
-      <c r="O32" t="s">
-        <v>25</v>
-      </c>
-      <c r="V32" t="s">
-        <v>25</v>
-      </c>
-      <c r="W32" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+      <c r="K32" t="s">
+        <v>20</v>
+      </c>
+      <c r="T32" t="s">
+        <v>20</v>
+      </c>
+      <c r="U32" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E33">
         <v>2022</v>
@@ -2255,27 +2279,30 @@
         <v>6375</v>
       </c>
       <c r="H33" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J33" t="s">
-        <v>24</v>
-      </c>
-      <c r="O33" t="s">
-        <v>25</v>
-      </c>
-      <c r="W33" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+      <c r="N33" t="s">
+        <v>20</v>
+      </c>
+      <c r="U33" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>111</v>
+        <v>106</v>
+      </c>
+      <c r="B34" t="s">
+        <v>106</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D34" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E34">
         <v>2014</v>
@@ -2285,39 +2312,36 @@
         <v>2014</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H34" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J34" t="s">
-        <v>24</v>
-      </c>
-      <c r="O34" t="s">
-        <v>25</v>
-      </c>
-      <c r="P34" t="s">
-        <v>25</v>
-      </c>
-      <c r="W34" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+      <c r="M34" t="s">
+        <v>20</v>
+      </c>
+      <c r="U34" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C35" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E35" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="F35">
         <v>20241</v>
@@ -2326,27 +2350,27 @@
         <v>5075</v>
       </c>
       <c r="I35" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K35" t="s">
-        <v>25</v>
-      </c>
-      <c r="W35" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:24" ht="42.75" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U35" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C36" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E36">
         <v>2023</v>
@@ -2359,27 +2383,27 @@
         <v>4400</v>
       </c>
       <c r="I36" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N36" t="s">
-        <v>25</v>
-      </c>
-      <c r="W36" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C37" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D37" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E37">
         <v>2022</v>
@@ -2392,30 +2416,30 @@
         <v>7000</v>
       </c>
       <c r="I37" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L37" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M37" t="s">
-        <v>25</v>
-      </c>
-      <c r="T37" t="s">
-        <v>25</v>
-      </c>
-      <c r="W37" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="R37" t="s">
+        <v>20</v>
+      </c>
+      <c r="U37" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D38" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E38">
         <v>2023</v>
@@ -2428,36 +2452,36 @@
         <v>13200</v>
       </c>
       <c r="I38" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L38" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M38" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="R38" t="s">
+        <v>20</v>
       </c>
       <c r="T38" t="s">
-        <v>25</v>
-      </c>
-      <c r="V38" t="s">
-        <v>25</v>
-      </c>
-      <c r="W38" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C39" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D39" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E39">
         <v>2023</v>
@@ -2470,30 +2494,30 @@
         <v>3400</v>
       </c>
       <c r="I39" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L39" t="s">
-        <v>25</v>
-      </c>
-      <c r="V39" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="T39" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B40" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E40" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="F40">
         <v>20243</v>
@@ -2503,30 +2527,30 @@
         <v>12600</v>
       </c>
       <c r="I40" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L40" t="s">
-        <v>25</v>
-      </c>
-      <c r="W40" t="s">
-        <v>25</v>
-      </c>
-      <c r="X40" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U40" t="s">
+        <v>20</v>
+      </c>
+      <c r="V40" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B41" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E41">
         <v>2022</v>
@@ -2539,30 +2563,30 @@
         <v>6300</v>
       </c>
       <c r="I41" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L41" t="s">
-        <v>25</v>
-      </c>
-      <c r="W41" t="s">
-        <v>25</v>
-      </c>
-      <c r="X41" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U41" t="s">
+        <v>20</v>
+      </c>
+      <c r="V41" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B42" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C42" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D42" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E42">
         <v>2022</v>
@@ -2575,27 +2599,27 @@
         <v>3570</v>
       </c>
       <c r="I42" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L42" t="s">
-        <v>25</v>
-      </c>
-      <c r="W42" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+      <c r="U42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B43" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D43" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E43">
         <v>2024</v>
@@ -2607,48 +2631,42 @@
         <v>48400</v>
       </c>
       <c r="H43" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I43" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J43" t="s">
-        <v>24</v>
-      </c>
-      <c r="L43" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="N43" t="s">
-        <v>25</v>
-      </c>
-      <c r="O43" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q43" s="4">
+        <v>20</v>
+      </c>
+      <c r="O43" s="4">
         <v>45310</v>
       </c>
-      <c r="R43" s="4">
+      <c r="P43" s="4">
         <v>45657</v>
       </c>
-      <c r="S43" t="s">
-        <v>136</v>
-      </c>
-      <c r="W43" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="Q43" t="s">
+        <v>131</v>
+      </c>
+      <c r="U43" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B44" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C44" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D44" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E44">
         <v>2024</v>
@@ -2660,36 +2678,36 @@
         <v>9750</v>
       </c>
       <c r="I44" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L44" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="M44" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q44" s="4">
+        <v>20</v>
+      </c>
+      <c r="O44" s="4">
         <v>45323</v>
       </c>
-      <c r="R44" s="4">
+      <c r="P44" s="4">
         <v>45627</v>
       </c>
-      <c r="S44" t="s">
-        <v>136</v>
-      </c>
-      <c r="W44" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="Q44" t="s">
+        <v>131</v>
+      </c>
+      <c r="U44" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B45" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D45" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E45">
         <v>2024</v>
@@ -2702,42 +2720,39 @@
         <v>16000</v>
       </c>
       <c r="I45" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L45" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="N45" t="s">
-        <v>25</v>
-      </c>
-      <c r="O45" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q45" s="4">
+        <v>20</v>
+      </c>
+      <c r="O45" s="4">
         <v>45323</v>
       </c>
-      <c r="R45" s="4">
+      <c r="P45" s="4">
         <v>45473</v>
       </c>
-      <c r="W45" t="s">
-        <v>25</v>
-      </c>
-      <c r="X45" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="U45" t="s">
+        <v>20</v>
+      </c>
+      <c r="V45" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B46" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C46" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D46" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E46">
         <v>2024</v>
@@ -2749,42 +2764,39 @@
         <v>17213</v>
       </c>
       <c r="H46" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I46" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J46" t="s">
-        <v>24</v>
-      </c>
-      <c r="L46" t="s">
-        <v>25</v>
-      </c>
-      <c r="O46" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q46" s="4">
+        <v>19</v>
+      </c>
+      <c r="N46" t="s">
+        <v>20</v>
+      </c>
+      <c r="O46" s="4">
         <v>45323</v>
       </c>
-      <c r="R46" s="4">
+      <c r="P46" s="4">
         <v>45566</v>
       </c>
-      <c r="W46" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="U46" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B47" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D47" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E47" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F47">
         <v>2023</v>
@@ -2793,39 +2805,39 @@
         <v>184000</v>
       </c>
       <c r="H47" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J47" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M47" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q47" s="4">
+        <v>20</v>
+      </c>
+      <c r="O47" s="4">
         <v>45108</v>
       </c>
-      <c r="R47" s="4">
+      <c r="P47" s="4">
         <v>46053</v>
       </c>
+      <c r="T47" t="s">
+        <v>20</v>
+      </c>
+      <c r="U47" t="s">
+        <v>20</v>
+      </c>
       <c r="V47" t="s">
-        <v>25</v>
-      </c>
-      <c r="W47" t="s">
-        <v>25</v>
-      </c>
-      <c r="X47" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D48" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="E48">
         <v>2024</v>
@@ -2838,33 +2850,33 @@
         <v>8000</v>
       </c>
       <c r="I48" t="s">
-        <v>24</v>
-      </c>
-      <c r="O48" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q48" s="4">
+        <v>19</v>
+      </c>
+      <c r="N48" t="s">
+        <v>20</v>
+      </c>
+      <c r="O48" s="4">
         <v>45566</v>
       </c>
-      <c r="R48" s="4">
+      <c r="P48" s="4">
         <v>45657</v>
       </c>
-      <c r="V48" t="s">
-        <v>25</v>
-      </c>
-      <c r="W48" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="T48" t="s">
+        <v>20</v>
+      </c>
+      <c r="U48" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D49" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E49">
         <v>2024</v>
@@ -2876,39 +2888,36 @@
         <v>16200</v>
       </c>
       <c r="I49" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N49" t="s">
-        <v>25</v>
-      </c>
-      <c r="O49" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q49" s="4">
+        <v>20</v>
+      </c>
+      <c r="O49" s="4">
         <v>45536</v>
       </c>
-      <c r="R49" s="4">
+      <c r="P49" s="4">
         <v>45657</v>
       </c>
+      <c r="T49" t="s">
+        <v>20</v>
+      </c>
+      <c r="U49" t="s">
+        <v>20</v>
+      </c>
       <c r="V49" t="s">
-        <v>25</v>
-      </c>
-      <c r="W49" t="s">
-        <v>25</v>
-      </c>
-      <c r="X49" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D50" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="E50">
         <v>2025</v>
@@ -2920,33 +2929,33 @@
         <v>1700</v>
       </c>
       <c r="I50" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M50" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q50" s="4">
+        <v>20</v>
+      </c>
+      <c r="O50" s="4">
         <v>45689</v>
       </c>
-      <c r="R50" s="4">
+      <c r="P50" s="4">
         <v>45703</v>
       </c>
-      <c r="W50" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="U50" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C51" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D51" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E51">
         <v>2025</v>
@@ -2959,30 +2968,30 @@
         <v>1875</v>
       </c>
       <c r="I51" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q51" s="4">
+        <v>19</v>
+      </c>
+      <c r="O51" s="4">
         <v>45690</v>
       </c>
-      <c r="R51" s="4">
+      <c r="P51" s="4">
         <v>45746</v>
       </c>
-      <c r="W51" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="U51" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B52" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C52" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D52" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E52">
         <v>2025</v>
@@ -2994,36 +3003,33 @@
         <v>24000</v>
       </c>
       <c r="H52" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I52" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N52" t="s">
-        <v>25</v>
-      </c>
-      <c r="O52" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q52" s="4">
+        <v>20</v>
+      </c>
+      <c r="O52" s="4">
         <v>45718</v>
       </c>
-      <c r="V52" t="s">
-        <v>25</v>
-      </c>
-      <c r="W52" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="T52" t="s">
+        <v>20</v>
+      </c>
+      <c r="U52" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B53" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D53" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="E53">
         <v>2025</v>
@@ -3035,30 +3041,30 @@
         <v>4250</v>
       </c>
       <c r="I53" t="s">
-        <v>24</v>
-      </c>
-      <c r="O53" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q53" s="4">
+        <v>19</v>
+      </c>
+      <c r="N53" t="s">
+        <v>20</v>
+      </c>
+      <c r="O53" s="4">
         <v>45901</v>
       </c>
-      <c r="R53" s="4">
+      <c r="P53" s="4">
         <v>46022</v>
       </c>
-      <c r="V53" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:24" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="T53" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="E54">
         <v>2025</v>
@@ -3070,33 +3076,33 @@
         <v>3000</v>
       </c>
       <c r="I54" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="M54" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q54" s="4">
+        <v>20</v>
+      </c>
+      <c r="O54" s="4">
         <v>45901</v>
       </c>
-      <c r="R54" s="4">
+      <c r="P54" s="4">
         <v>46022</v>
       </c>
-      <c r="V54" t="s">
-        <v>25</v>
-      </c>
-      <c r="W54" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="T54" t="s">
+        <v>20</v>
+      </c>
+      <c r="U54" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B55" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D55" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E55">
         <v>2025</v>
@@ -3109,19 +3115,183 @@
         <v>2975</v>
       </c>
       <c r="I55" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q55" s="4">
+        <v>19</v>
+      </c>
+      <c r="O55" s="4">
         <v>45931</v>
       </c>
-      <c r="R55" s="4">
+      <c r="P55" s="4">
         <v>46052</v>
       </c>
-      <c r="W55" t="s">
-        <v>25</v>
+      <c r="U55" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>163</v>
+      </c>
+      <c r="D56" t="s">
+        <v>164</v>
+      </c>
+      <c r="E56">
+        <v>2025</v>
+      </c>
+      <c r="F56">
+        <f t="shared" ref="F56" si="1">E56</f>
+        <v>2025</v>
+      </c>
+      <c r="G56" s="1">
+        <v>82500</v>
+      </c>
+      <c r="H56" t="s">
+        <v>19</v>
+      </c>
+      <c r="J56" t="s">
+        <v>19</v>
+      </c>
+      <c r="L56" t="s">
+        <v>20</v>
+      </c>
+      <c r="M56" t="s">
+        <v>20</v>
+      </c>
+      <c r="N56" t="s">
+        <v>20</v>
+      </c>
+      <c r="O56" s="4">
+        <v>45717</v>
+      </c>
+      <c r="U56" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>51</v>
+      </c>
+      <c r="C57" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" t="s">
+        <v>170</v>
+      </c>
+      <c r="E57">
+        <v>2026</v>
+      </c>
+      <c r="F57">
+        <v>2026</v>
+      </c>
+      <c r="G57" s="1">
+        <v>800</v>
+      </c>
+      <c r="H57" t="s">
+        <v>19</v>
+      </c>
+      <c r="J57" t="s">
+        <v>19</v>
+      </c>
+      <c r="L57" t="s">
+        <v>20</v>
+      </c>
+      <c r="O57" s="4">
+        <v>46174</v>
+      </c>
+      <c r="P57" s="4">
+        <v>46204</v>
+      </c>
+      <c r="T57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>166</v>
+      </c>
+      <c r="C58" t="s">
+        <v>165</v>
+      </c>
+      <c r="D58" t="s">
+        <v>169</v>
+      </c>
+      <c r="E58">
+        <v>2026</v>
+      </c>
+      <c r="F58">
+        <v>2026</v>
+      </c>
+      <c r="G58" s="1">
+        <v>800</v>
+      </c>
+      <c r="H58" t="s">
+        <v>19</v>
+      </c>
+      <c r="J58" t="s">
+        <v>19</v>
+      </c>
+      <c r="N58" t="s">
+        <v>20</v>
+      </c>
+      <c r="O58" s="4">
+        <v>46174</v>
+      </c>
+      <c r="P58" s="4">
+        <v>46204</v>
+      </c>
+      <c r="U58" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>167</v>
+      </c>
+      <c r="C59" t="s">
+        <v>84</v>
+      </c>
+      <c r="D59" t="s">
+        <v>168</v>
+      </c>
+      <c r="E59">
+        <v>2026</v>
+      </c>
+      <c r="F59">
+        <v>2026</v>
+      </c>
+      <c r="G59" s="1">
+        <v>13340</v>
+      </c>
+      <c r="H59" t="s">
+        <v>19</v>
+      </c>
+      <c r="J59" t="s">
+        <v>19</v>
+      </c>
+      <c r="N59" t="s">
+        <v>20</v>
+      </c>
+      <c r="O59" s="4">
+        <v>46082</v>
+      </c>
+      <c r="P59" s="4"/>
+      <c r="U59" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:W59" xr:uid="{D9B3B7FE-E50F-4A1F-B29E-52CC043F3381}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I34">
     <sortCondition ref="E2:E34"/>
   </sortState>
